--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/KANSAS_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/KANSAS_2010.xlsx
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C152">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C185">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C520">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C815">
